--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_xgb_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_xgb_quarterly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>2.084184136156412</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -958,27 +959,27 @@
         <v>0.7822599407481463</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -986,19 +987,19 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
@@ -1006,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1095,19 +1096,19 @@
         <v>1.527420507440588</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
@@ -1115,7 +1116,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1123,19 +1124,19 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
@@ -1143,7 +1144,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1236,27 +1237,27 @@
         <v>1.650005263820381</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1266,19 +1267,19 @@
         <v>-0.0004656900454867996</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1286,15 +1287,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AL6" s="2" t="n">
@@ -1302,15 +1303,15 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -1393,27 +1394,27 @@
         <v>2.438839629687553</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1421,19 +1422,19 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1534,27 +1535,27 @@
         <v>2.154174062269041</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1568,15 +1569,15 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1584,31 +1585,31 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1691,19 +1692,19 @@
         <v>2.327996341529066</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
@@ -1711,7 +1712,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1719,19 +1720,19 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
@@ -1739,7 +1740,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1832,27 +1833,27 @@
         <v>2.074842337306634</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="n">
@@ -1862,19 +1863,19 @@
         <v>-0.0110007159717862</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH10" s="2" t="n">
@@ -1882,31 +1883,31 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -2151,28 +2152,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196766695</v>
+        <v>0.05644008609220919</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208211</v>
+        <v>0.08831268540851211</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571158</v>
+        <v>0.2970580221997945</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798214</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2181,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278878</v>
+        <v>0.272403402144199</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2193,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.139529174066894</v>
+        <v>-0.08310591627222996</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2239,49 +2240,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.1143103961605181</v>
+        <v>0.09041417313448719</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.2291518234198189</v>
+        <v>0.03215902869413889</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2005953685030064</v>
+        <v>0.08759061925316305</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2047065010143791</v>
+        <v>0.3130992931150791</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9806094182825484</v>
+        <v>0.9</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.4742034398605797</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.007071403074654037</v>
+        <v>-0.008548633056465471</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.007959461392532</v>
+        <v>1.041817836506867</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.119280498649606</v>
+        <v>0.324646577182107</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.2379055525502543</v>
+        <v>0.04105865714432233</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.572047799034418</v>
+        <v>1.191786059302786</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1469831993585559</v>
+        <v>-0.08202293348751755</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2333,58 +2334,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.3232523550594082</v>
+        <v>0.07226254240722541</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.4596274527008404</v>
+        <v>0.01497714496384162</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1029240628466189</v>
+        <v>0.080664311843716</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1531765783358609</v>
+        <v>0.2791637973599133</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9484764542936288</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2531143766379184</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.4104392274304347</v>
+        <v>0.009378627607342649</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.538015984914983</v>
+        <v>0.9541220317503244</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.7716934342675263</v>
+        <v>0.2794607860995721</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.03487440246540663</v>
+        <v>0.005546498809638756</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.083856072122412</v>
+        <v>1.0259078407238</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.05531518128978974</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.1875078610222278</v>
+        <v>-0.01664654694929668</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.4204840426571776</v>
+        <v>0.0180818356416963</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1640118259963984</v>
+        <v>-0.03411158256163516</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2435,58 +2436,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.09634280925647731</v>
+        <v>-0.132270622788212</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.2093324873697813</v>
+        <v>-0.1786288795405951</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1761854474856462</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1013013481462895</v>
+        <v>0.1144200239856831</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1069926439383044</v>
+        <v>0.2758955938241937</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9761772853185595</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1190433501409357</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.6636226187266634</v>
+        <v>-0.008548633056465471</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.2530366948111946</v>
+        <v>1.041817836506867</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1761854474856462</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2444912124017347</v>
+        <v>0.05412675088384966</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2730728268798097</v>
+        <v>-0.1715467365872482</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.3433919136473099</v>
+        <v>0.198700715401481</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07210823088668705</v>
+        <v>-0.06119825830416614</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.01612440031606099</v>
+        <v>-0.2042203792001098</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.6754705462992563</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.4127765469484961</v>
+        <v>-0.2042203792001097</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2541,67 +2542,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1027336580832536</v>
+        <v>0.06305230176887155</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2163819805053555</v>
+        <v>0.006258959465577529</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4047059514853544</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1768438251943143</v>
+        <v>0.08636592444278221</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1675749411347852</v>
+        <v>0.3050396014238048</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9795013850415513</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.367752835996173</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1939528271122346</v>
+        <v>-0.008548633056465471</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7816897123421588</v>
+        <v>1.041817836506867</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4047059514853544</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.7441496314510616</v>
+        <v>0.2914070887906723</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.01878562777674353</v>
+        <v>0.01493526865336037</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.04517034977944</v>
+        <v>1.069763029745178</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.06736803220005649</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.01038915020191267</v>
+        <v>-0.02509309952103944</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2024558773001104</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1770085967561046</v>
+        <v>-0.02509309952103933</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.166649011530574</v>
+        <v>-0.008589538731509583</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.1534886410615501</v>
+        <v>-0.01776068976842049</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.01554659642787026</v>
+        <v>0.009336982282605488</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -2649,58 +2650,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.2827548267079446</v>
+        <v>-0.132270622788212</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.2088351543441962</v>
+        <v>-0.1786288795405951</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.6243314085866118</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.4165533241636485</v>
+        <v>0.1144200239856831</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1825499726065928</v>
+        <v>0.2758955938241937</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9983379501385041</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.5849665093610337</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.2162394112507975</v>
+        <v>-0.008548633056465471</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.24339572037177</v>
+        <v>1.041817836506867</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.6049777689466195</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.7281621591255638</v>
+        <v>0.05412675088384966</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.009447090110026979</v>
+        <v>-0.1715467365872482</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.022715682953971</v>
+        <v>0.198700715401481</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1255402942745092</v>
+        <v>-0.06119825830416614</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.3563326917137232</v>
+        <v>-0.2042203792001098</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.2106576533537687</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1845524175649521</v>
+        <v>-0.2042203792001097</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2755,67 +2756,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.1128532534881675</v>
+        <v>0.06305230176887155</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.02142343383566581</v>
+        <v>0.006258959465577529</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.5479825620901642</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.3160195933706594</v>
+        <v>0.08636592444278221</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1917579273185493</v>
+        <v>0.3050396014238048</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9983379501385041</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.5454487668652108</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1416130260959952</v>
+        <v>-0.008548633056465471</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.159397421132842</v>
+        <v>1.041817836506867</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.5479825620901642</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.9516980305908982</v>
+        <v>0.2914070887906723</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.1400179591655482</v>
+        <v>0.01493526865336037</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.336675476916511</v>
+        <v>1.069763029745178</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1255402942745091</v>
+        <v>-0.06736803220005649</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.2038602982000379</v>
+        <v>-0.02509309952103944</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-0.1354997967003431</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.07907517110901097</v>
+        <v>-0.02509309952103933</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.3295710050166482</v>
+        <v>-0.008589538731509583</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.3914044949899539</v>
+        <v>-0.01776068976842049</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.1016003067132161</v>
+        <v>0.009336982282605488</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -2863,64 +2864,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.07574116126794583</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.01951345051952513</v>
+        <v>-0.03796582501302315</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.4260784533960039</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.2854767045319356</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1300913453827354</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9955678670360111</v>
+        <v>0</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.4000728426920627</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1329188429936279</v>
+        <v>0.2117597153840087</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.8503886162365928</v>
+        <v>-0.03587709265072071</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.4260784533960039</v>
+        <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.5406184358772748</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1001001909143288</v>
+        <v>-0.2060850325577076</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7593074508701473</v>
+        <v>0.03737143334716841</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.07583311175651308</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1705553121314384</v>
+        <v>-0.06793997025427589</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1409872235544114</v>
+        <v>0.2222079224315814</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2730464717346531</v>
+        <v>-0.2373965078778153</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.05783218662559397</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.05280264614878494</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2969,70 +2974,74 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.03353104152917252</v>
+        <v>0.07226254240722541</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.06607376784443697</v>
+        <v>0.01497714496384162</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.5258737762823344</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.2717946635040229</v>
+        <v>0.080664311843716</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1748523052402025</v>
+        <v>0.2791637973599133</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9961218836565097</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.4885252850006722</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.03411716692781308</v>
+        <v>0.009378627607342649</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.038401752822976</v>
+        <v>0.9541220317503244</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.5258737762823344</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.8895732870628756</v>
+        <v>0.2794607860995721</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.1037299052656031</v>
+        <v>0.005546498809638756</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1.249420256757994</v>
+        <v>1.0259078407238</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.05531518128978974</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.1326752745007989</v>
+        <v>-0.01664654694929668</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>-0.02723837739884583</v>
+        <v>0.0180818356416963</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.108389244242609</v>
+        <v>-0.03411158256163516</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.2696261187251487</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.3151900384734401</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.06653512990190902</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.05783218662559397</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>-0.01680153018289654</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3275,28 +3284,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.05341499464255506</v>
+        <v>-0.09123360655355239</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2216991067360366</v>
+        <v>0.2716992530341484</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389480542019927</v>
+        <v>0.1810585772249194</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.5035092528573126</v>
+        <v>-0.4707583434268603</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3305,10 +3314,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.12172130237064</v>
+        <v>0.7171104771509207</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3317,7 +3326,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756415</v>
+        <v>-0.139529174066894</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3363,49 +3372,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.07794149969959396</v>
+        <v>0.1137402955357241</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.0232828516603385</v>
+        <v>0.2255518068971762</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4771343763893187</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2188856193116722</v>
+        <v>0.2007065323816303</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2809242913791384</v>
+        <v>0.2048198630871046</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9825581395348837</v>
+        <v>0.9811425402107599</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.5468101317287758</v>
+        <v>-0.4746076449481669</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.08721386877934878</v>
+        <v>-0.007273239877282123</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.085998179031943</v>
+        <v>1.008176809981286</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4771343763893187</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.378564869094712</v>
+        <v>1.119825849818175</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1210543375499389</v>
+        <v>0.2345308458751303</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.228972710227808</v>
+        <v>1.561580656675442</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1959907093589865</v>
+        <v>-0.1469831993585559</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3457,58 +3466,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.2802901328432288</v>
+        <v>0.3294578948487177</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.21537109245123</v>
+        <v>0.4629259009092757</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1663071666219633</v>
+        <v>0.1029808820995737</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2118385751587301</v>
+        <v>0.1532558675077065</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9462209302325582</v>
+        <v>0.9484193011647255</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.4439839127181155</v>
+        <v>-0.2514292974161799</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1198921439760285</v>
+        <v>0.414421357968767</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.8817790541059516</v>
+        <v>0.5340941927569753</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.302613471315189</v>
+        <v>0.7759950933958086</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.08525727141563522</v>
+        <v>0.03429285245675695</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.16126302367821</v>
+        <v>1.082113730200731</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1240889646699911</v>
+        <v>-0.1209745732692815</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.1877176388514834</v>
+        <v>0.1936875231844157</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.2268943465195057</v>
+        <v>0.4247841549007105</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.0319316066449894</v>
+        <v>-0.1621976430053712</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3559,68 +3568,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.06359365361642944</v>
+        <v>0.09529483681114836</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.11107554843444</v>
+        <v>0.2052545568474442</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2597750654112301</v>
+        <v>-0.1761854474856462</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.09923504537432014</v>
+        <v>0.1013540872965955</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.09710573882619537</v>
+        <v>0.1070516526527635</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3590116279069768</v>
+        <v>0.9767054908485857</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>-0.1197205838598523</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1.058870045499049</v>
+        <v>0.6632844471087009</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.04411026616389809</v>
+        <v>0.2543143112203868</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1761854474856462</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>-0.08393929514495979</v>
+        <v>0.2442581488657329</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.5682464497898438</v>
+        <v>-0.2753767649649183</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-0.07483079350241714</v>
+        <v>0.3406143915734858</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.2597750654112301</v>
+        <v>-0.07210823088668705</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1313013306895292</v>
+        <v>-0.01656172340940865</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>1.255588658808566</v>
+        <v>0.6754705462992563</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.61486831124194</v>
+        <v>-0.4130375620372505</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.1265041286974922</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.0912732381757877</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3669,74 +3674,70 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.08735839521504718</v>
+        <v>0.1045613049727521</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.03222224929882445</v>
+        <v>0.2154513117323396</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.4047059514853544</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1732993881163748</v>
+        <v>0.1769418175779841</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2198739246763722</v>
+        <v>0.167665132053837</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9796511627906976</v>
+        <v>0.9800332778702163</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4439839127181155</v>
+        <v>-0.3682388747793769</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1198921439760285</v>
+        <v>0.1937101272626591</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8817790541059516</v>
+        <v>0.7822248504377036</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.4047059514853544</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.9556239829870019</v>
+        <v>0.7483844144209064</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.07828423044914257</v>
+        <v>0.018213118891381</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.8519263929171988</v>
+        <v>1.043611044973485</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1960033010979126</v>
+        <v>-0.1209745732692815</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.008735998677180223</v>
+        <v>-0.008241589713297359</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2268943465195057</v>
+        <v>0.2024558773001104</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1778134755133596</v>
+        <v>-0.1752226181358851</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.1506937628268092</v>
+        <v>-0.1691641312954535</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1560434798743909</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.1506937628268091</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.1265041286974922</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.002061632408944414</v>
-      </c>
+        <v>-0.01554659642787015</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3781,58 +3782,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.04667538669436389</v>
+        <v>-0.2831217818425582</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.006397865971594641</v>
+        <v>-0.2111523672891118</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3235130044559731</v>
+        <v>-0.6243314085866118</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1256447961333834</v>
+        <v>0.4167294808017777</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1682944502993051</v>
+        <v>0.1826508985909507</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.970203488372093</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3235130044559731</v>
+        <v>-0.5852855655533962</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3625369645602079</v>
+        <v>-0.2163987295862236</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.6425165031627573</v>
+        <v>1.24328240534802</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3235130044559731</v>
+        <v>-0.6049777689466196</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5472217405341748</v>
+        <v>0.7286068644175512</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2707705112799527</v>
+        <v>0.00669519371036964</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.4878410879580152</v>
+        <v>1.016031542744021</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.2597750654112309</v>
+        <v>-0.1255402942745092</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.02900538945197251</v>
+        <v>-0.3563326917137233</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.4927231231461782</v>
+        <v>-0.2106576533537688</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.3495145914927047</v>
+        <v>-0.1845524175649522</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3887,67 +3888,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.06424194128360572</v>
+        <v>-0.1133071332295871</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.01027794999702314</v>
+        <v>-0.02428954991647747</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4853919564080009</v>
+        <v>-0.5479825620901643</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1848094113550131</v>
+        <v>0.3161825582834581</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2363436358893351</v>
+        <v>0.1918640440515781</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9847383720930233</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4853919564080009</v>
+        <v>-0.5457982022456046</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.03649070310690994</v>
+        <v>-0.1417875140529004</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9640179473435697</v>
+        <v>1.159402079360921</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4853919564080009</v>
+        <v>-0.5479825620901643</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.068063168727649</v>
+        <v>0.9522002580224977</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.02528990663525776</v>
+        <v>0.1369101079982022</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.9521644694367576</v>
+        <v>1.327829237421811</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1960033010979126</v>
+        <v>-0.1255402942745091</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.01270899990380381</v>
+        <v>-0.203860298200038</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1355241580202704</v>
+        <v>-0.1354997967003428</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1305416154091439</v>
+        <v>-0.07907517110901097</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.1687493998566012</v>
+        <v>-0.3330417832666209</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.07447274393140479</v>
+        <v>-0.3932412847755863</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.101862646731399</v>
+        <v>0.09921489382595894</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -3995,58 +3996,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.01380020960836703</v>
+        <v>-0.07621402820273182</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.06380695603609621</v>
+        <v>0.01652743593858008</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2272156375034153</v>
+        <v>-0.4260784533960038</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1148020975365047</v>
+        <v>0.2856227920208648</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1297887850437884</v>
+        <v>0.1301631387026728</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9840116279069767</v>
+        <v>0.9961175818080976</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.0735381990325833</v>
+        <v>-0.4005340355326953</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.8660202759048783</v>
+        <v>0.1326885497805863</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.146051335929318</v>
+        <v>0.8508272686513193</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1139983911416499</v>
+        <v>-0.4260784533960038</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.06447971126476837</v>
+        <v>0.5410148808334092</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.498294281121934</v>
+        <v>-0.102553445838671</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.05748282673111162</v>
+        <v>0.7544372841725321</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.2272156375034154</v>
+        <v>-0.07583311175651308</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.08510824505182146</v>
+        <v>-0.1705553121314384</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>1.044312695033486</v>
+        <v>0.1409872235544116</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.5524697580899224</v>
+        <v>-0.2730464717346531</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -4101,67 +4102,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.09117302493297164</v>
+        <v>-0.03402550389707903</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.03584345246882359</v>
+        <v>0.06295138450214322</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.4592803435105396</v>
+        <v>-0.5258737762823346</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1915169822424543</v>
+        <v>0.2719423346117652</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2249188632402941</v>
+        <v>0.174949039769716</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9811046511627907</v>
+        <v>0.9966722129783694</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.4592803435105396</v>
+        <v>-0.4889184801975371</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.08908304857907456</v>
+        <v>-0.03431350602343819</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.9121586960005542</v>
+        <v>1.038576346068518</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.4592803435105396</v>
+        <v>-0.5258737762823346</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>1.018001402089293</v>
+        <v>0.890059528030436</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.04888478998889201</v>
+        <v>0.1007209804965359</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.9075350534378316</v>
+        <v>1.241174904551167</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1960033010979124</v>
+        <v>-0.1209745732692815</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.01227480826841254</v>
+        <v>-0.132675274500799</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1931415381198494</v>
+        <v>-0.02723837739884594</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.1515886624284711</v>
+        <v>-0.1083892442426091</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.1477142587128057</v>
+        <v>-0.2734072287314961</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.02751077017789449</v>
+        <v>-0.3172568495689486</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.1236039277852975</v>
+        <v>0.06422564738989744</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -4407,28 +4408,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093225</v>
+        <v>0.05341499464255506</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.08126757478702572</v>
+        <v>0.2216991067360366</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962868</v>
+        <v>0.2389480542019927</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4437,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165614</v>
+        <v>1.12172130237064</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4449,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756415</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4495,49 +4496,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.07836937291241863</v>
+        <v>0.07794149969959396</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.05370233749755293</v>
+        <v>0.0232828516603385</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.04064383247477164</v>
+        <v>0.2188856193116722</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1705705942703356</v>
+        <v>0.2809242913791384</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.8482758620689655</v>
+        <v>0.9825581395348837</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1377043507659563</v>
+        <v>-0.5468101317287758</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.0717563562167709</v>
+        <v>-0.08721386877934878</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.7045976084874375</v>
+        <v>1.085998179031943</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2505796287738526</v>
+        <v>1.378564869094712</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.01684526395807662</v>
+        <v>0.1210543375499389</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9212251943636144</v>
+        <v>1.228972710227808</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.02590709634784172</v>
+        <v>-0.1959907093589865</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4589,58 +4590,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.02427859728711668</v>
+        <v>0.2802901328432288</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.0008488550590588506</v>
+        <v>0.21537109245123</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04278454166173134</v>
+        <v>0.1663071666219633</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1644125150610335</v>
+        <v>0.2118385751587301</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9241379310344827</v>
+        <v>0.9462209302325582</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181155</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07145768887935322</v>
+        <v>0.1198921439760285</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7058271448015913</v>
+        <v>0.8817790541059516</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1881819355445027</v>
+        <v>1.302613471315189</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06589978732071489</v>
+        <v>0.08525727141563522</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.6918277475147857</v>
+        <v>1.16126302367821</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1240889646699911</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.05015978474909355</v>
+        <v>0.1877176388514834</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>-0.0002786709271050958</v>
+        <v>0.2268943465195057</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.04989501811294383</v>
+        <v>-0.0319316066449894</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4691,67 +4692,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.07864266648964202</v>
+        <v>-0.06359365361642944</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.05396937965247406</v>
+        <v>-0.11107554843444</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.2597750654112301</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.04063637981497253</v>
+        <v>0.09923504537432014</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.170283088592917</v>
+        <v>0.09710573882619537</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8137931034482758</v>
+        <v>0.3590116279069768</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1374858172388338</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.07202797384228954</v>
+        <v>1.058870045499049</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7034794288531094</v>
+        <v>-0.04411026616389809</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>0</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2505796287738526</v>
+        <v>-0.08393929514495979</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.01684526395807662</v>
+        <v>-0.5682464497898438</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9212251943636144</v>
+        <v>-0.07483079350241714</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.02590709634784172</v>
+        <v>-0.2597750654112301</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.0002534322506630993</v>
+        <v>-0.1313013306895292</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.0002534322506633213</v>
+        <v>1.255588658808566</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.61486831124194</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.1436226220825925</v>
+        <v>0.1265041286974922</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.117446750589972</v>
+        <v>-0.0912732381757877</v>
       </c>
     </row>
     <row r="6">
@@ -4801,73 +4802,73 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.07244167405127921</v>
+        <v>0.08735839521504718</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.04791023109796644</v>
+        <v>0.03222224929882445</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1461625015373461</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.04067966124234599</v>
+        <v>0.1732993881163748</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1707473967157109</v>
+        <v>0.2198739246763722</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.8551724137931035</v>
+        <v>0.9796511627906976</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1424443119205702</v>
+        <v>-0.4439839127181155</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.06586500850999477</v>
+        <v>0.1198921439760285</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7288507658879655</v>
+        <v>0.8817790541059516</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1461625015373461</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2505796287738526</v>
+        <v>0.9556239829870019</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.01684526395807662</v>
+        <v>-0.07828423044914257</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9212251943636144</v>
+        <v>0.8519263929171988</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.02590709634784172</v>
+        <v>-0.1960033010979126</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.005496909509892789</v>
+        <v>0.008735998677180223</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>-0.005496909509892789</v>
+        <v>0.2268943465195057</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1778134755133596</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.04702146163331555</v>
+        <v>-0.1506937628268092</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.005219693159519756</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.05251526837996856</v>
+        <v>-0.1506937628268091</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.1436226220825925</v>
+        <v>0.1265041286974922</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.01922590984037953</v>
+        <v>-0.002061632408944414</v>
       </c>
     </row>
     <row r="7">
@@ -4913,58 +4914,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.03893753359674146</v>
+        <v>0.04667538669436389</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.0609212457552587</v>
+        <v>-0.006397865971594641</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.3235130044559731</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.06673151779653221</v>
+        <v>0.1256447961333834</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.143501989407793</v>
+        <v>0.1682944502993051</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.970203488372093</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1377043507659563</v>
+        <v>-0.3235130044559731</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.0717563562167709</v>
+        <v>0.3625369645602079</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.7045976084874375</v>
+        <v>0.6425165031627573</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.3235130044559731</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1145393894274509</v>
+        <v>0.5472217405341748</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1237945557331451</v>
+        <v>-0.2707705112799527</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.4210899816713415</v>
+        <v>0.4878410879580152</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.004518513181261619</v>
+        <v>-0.2597750654112309</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.108781749051665</v>
+        <v>-0.02900538945197251</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.4927231231461782</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1087817490516652</v>
+        <v>-0.3495145914927047</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5019,67 +5020,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.04565325715594182</v>
+        <v>0.06424194128360572</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.02173458274452567</v>
+        <v>0.01027794999702314</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.4853919564080009</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.04473739879544709</v>
+        <v>0.1848094113550131</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.163217008848222</v>
+        <v>0.2363436358893351</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9103448275862069</v>
+        <v>0.9847383720930233</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1377043507659563</v>
+        <v>-0.4853919564080009</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.0717563562167709</v>
+        <v>0.03649070310690994</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7045976084874375</v>
+        <v>0.9640179473435697</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.4853919564080009</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.2126389111260971</v>
+        <v>1.068063168727649</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.04667270987672878</v>
+        <v>-0.02528990663525776</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7817408110544962</v>
+        <v>0.9521644694367576</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1960033010979126</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.03033850606134925</v>
+        <v>-0.01270899990380381</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>0.1355241580202704</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03033850606134936</v>
+        <v>-0.1305416154091439</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.02086801376640857</v>
+        <v>-0.1687493998566012</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0.0002787486062376665</v>
+        <v>-0.07447274393140479</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.02058352753056014</v>
+        <v>-0.101862646731399</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -5127,58 +5128,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.03893753359674135</v>
+        <v>-0.01380020960836703</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.06092124575525859</v>
+        <v>-0.06380695603609621</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1461625015373466</v>
+        <v>-0.2272156375034153</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.06673151779653247</v>
+        <v>0.1148020975365047</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.143501989407793</v>
+        <v>0.1297887850437884</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9840116279069767</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.0735381990325833</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.0717563562167709</v>
+        <v>0.8660202759048783</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7045976084874369</v>
+        <v>0.146051335929318</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1461625015373466</v>
+        <v>-0.1139983911416499</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1145393894274509</v>
+        <v>0.06447971126476837</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1237945557331451</v>
+        <v>-0.498294281121934</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.4210899816713415</v>
+        <v>0.05748282673111162</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.004518513181261619</v>
+        <v>-0.2272156375034154</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1087817490516649</v>
+        <v>-0.08510824505182146</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>1.044312695033486</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1087817490516652</v>
+        <v>-0.5524697580899224</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5233,67 +5234,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.04565325715594182</v>
+        <v>0.09117302493297164</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.02173458274452567</v>
+        <v>0.03584345246882359</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.4592803435105396</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.04473739879544709</v>
+        <v>0.1915169822424543</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.163217008848222</v>
+        <v>0.2249188632402941</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9103448275862069</v>
+        <v>0.9811046511627907</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1377043507659563</v>
+        <v>-0.4592803435105396</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.0717563562167709</v>
+        <v>0.08908304857907456</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7045976084874375</v>
+        <v>0.9121586960005542</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.4592803435105396</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.2126389111260971</v>
+        <v>1.018001402089293</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.04667270987672878</v>
+        <v>-0.04888478998889201</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.7817408110544962</v>
+        <v>0.9075350534378316</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1960033010979124</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.03033850606134925</v>
+        <v>0.01227480826841254</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0</v>
+        <v>0.1931415381198494</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.03033850606134936</v>
+        <v>-0.1515886624284711</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.02086801376640857</v>
+        <v>-0.1477142587128057</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>0.0002787486062376665</v>
+        <v>-0.02751077017789449</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.02058352753056014</v>
+        <v>-0.1236039277852975</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -5539,28 +5540,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714512</v>
+        <v>0.0189121018756262</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570335</v>
+        <v>0.0809929380075199</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.4590501973559848</v>
+        <v>0.2138559415886582</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606708</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5569,10 +5570,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473776</v>
+        <v>0.2720069211165614</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5581,7 +5582,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.0518515658788602</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5627,49 +5628,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.002382745880526116</v>
+        <v>0.07634464914699279</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.08693880920546071</v>
+        <v>0.05636653757045784</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1335580210897492</v>
+        <v>0.0405134002783077</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4880113830458718</v>
+        <v>0.1700106362471846</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.8493150684931506</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1393233790300028</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.04246285263122429</v>
+        <v>0.07446620439756768</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.103849975367978</v>
+        <v>0.7002130779721872</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.474870734024246</v>
+        <v>0.2505796287738526</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.04644828317778826</v>
+        <v>-0.01684526395807662</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.868592529249625</v>
+        <v>0.9212251943636144</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.09631182261186377</v>
+        <v>-0.02590709634784172</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5721,58 +5722,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.007037250069187984</v>
+        <v>0.02497427700722055</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08269906430310359</v>
+        <v>0.005949654656603798</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1167974844615735</v>
+        <v>0.04263876767180749</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4296396949184721</v>
+        <v>0.1638459834801125</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.07691834452240665</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.6903412233993171</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.418854880877529</v>
+        <v>0.1881819355445027</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08266434720637639</v>
+        <v>-0.06589978732071489</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7661331690981564</v>
+        <v>0.6918277475147857</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07820336667939509</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.004643440051008918</v>
+        <v>-0.04772669440079758</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.04430638244290752</v>
+        <v>0.002282193813823996</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.03798017809593079</v>
+        <v>-0.04989501811294383</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5823,64 +5824,68 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.2557384680494813</v>
+        <v>0.07873461345690158</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.32205904040341</v>
+        <v>0.05871214157840843</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.242473557723479</v>
+        <v>0.04049792496675841</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4130524729380505</v>
+        <v>0.1696958601901456</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.8082191780821918</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1374122937580861</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.04246285263122429</v>
+        <v>0.07685199772384887</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.103849975367978</v>
+        <v>0.6906083231217613</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.09508025396987896</v>
+        <v>0.2505796287738526</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2919951341214182</v>
+        <v>-0.01684526395807662</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.1739125879110865</v>
+        <v>0.9212251943636144</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.05803005623353996</v>
+        <v>-0.02590709634784172</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2575076386647749</v>
+        <v>0.002220445200153076</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.002220445200153076</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.257507638664775</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.145773903183348</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.1191788981215037</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5929,70 +5934,74 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.03431627829690853</v>
+        <v>0.0731700656486507</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1203676115807562</v>
+        <v>0.05325087774808623</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1474954868777644</v>
+        <v>0.04054105892717042</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4623365257845903</v>
+        <v>0.170157790019918</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.8493150684931506</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1418618687233418</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.04246285263122429</v>
+        <v>0.07129716120614171</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.103849975367978</v>
+        <v>0.7129710493474782</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4208730799854183</v>
+        <v>0.2505796287738526</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.08135951609147174</v>
+        <v>-0.01684526395807662</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7698246845823712</v>
+        <v>0.9212251943636144</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.0782033666793952</v>
+        <v>-0.02590709634784172</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.03661178759137262</v>
+        <v>-0.002949411697134363</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>-0.002949411697134363</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.03661178759137274</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.04106454688071903</v>
+        <v>0.04702146163331533</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.04242661271423354</v>
+        <v>-0.005219693159519756</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.001422414043246834</v>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
+        <v>0.05251526837996856</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.145773903183348</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0.01662175333469529</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6037,58 +6046,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.2557384680494813</v>
+        <v>-0.04074200436961772</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.32205904040341</v>
+        <v>-0.05854686202610793</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.242473557723479</v>
+        <v>0.06650905459773392</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4130524729380505</v>
+        <v>0.1430218523324185</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.9794520547945206</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1393233790300028</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.04246285263122429</v>
+        <v>0.07446620439756768</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.103849975367978</v>
+        <v>0.7002130779721872</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.09508025396987896</v>
+        <v>0.1145393894274509</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2919951341214182</v>
+        <v>-0.1237945557331451</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.1739125879110865</v>
+        <v>0.4210899816713415</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.05803005623353996</v>
+        <v>-0.004518513181261619</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.2575076386647749</v>
+        <v>-0.1087817490516649</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.257507638664775</v>
+        <v>-0.1087817490516652</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6143,67 +6152,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.03431627829690853</v>
+        <v>0.04368996048474583</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1203676115807562</v>
+        <v>0.02431795496736977</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1474954868777644</v>
+        <v>0.04459228285718848</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4623365257845903</v>
+        <v>0.16267859865238</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.910958904109589</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1393233790300028</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.04246285263122429</v>
+        <v>0.07446620439756768</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.103849975367978</v>
+        <v>0.7002130779721872</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4208730799854183</v>
+        <v>0.2126389111260971</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.08135951609147174</v>
+        <v>-0.04667270987672878</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7698246845823712</v>
+        <v>0.7817408110544962</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.0782033666793952</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.03661178759137262</v>
+        <v>-0.03033850606134936</v>
       </c>
       <c r="Z8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03661178759137274</v>
+        <v>-0.03033850606134936</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.04106454688071903</v>
+        <v>0.01825966162992154</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.04242661271423354</v>
+        <v>-0.002276997264752278</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.001422414043246834</v>
+        <v>0.02058352753056014</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -6251,58 +6260,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.2557384680494816</v>
+        <v>-0.04074200436961761</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.3220590404034104</v>
+        <v>-0.05854686202610782</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3203589150179399</v>
+        <v>-0.1461625015373464</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.2424735577234793</v>
+        <v>0.06650905459773403</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4130524729380506</v>
+        <v>0.1430218523324186</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.9794520547945206</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.32035891501794</v>
+        <v>-0.1393233790300028</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-0.04246285263122473</v>
+        <v>0.07446620439756768</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.10384997536798</v>
+        <v>0.7002130779721872</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3203589150179399</v>
+        <v>-0.1461625015373464</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.09508025396987896</v>
+        <v>0.1145393894274509</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2919951341214182</v>
+        <v>-0.1237945557331451</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.1739125879110865</v>
+        <v>0.4210899816713415</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.05803005623353996</v>
+        <v>-0.004518513181261619</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.2575076386647752</v>
+        <v>-0.1087817490516648</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.257507638664775</v>
+        <v>-0.1087817490516652</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -6357,67 +6366,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.03431627829690853</v>
+        <v>0.04368996048474583</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.1203676115807562</v>
+        <v>0.02431795496736977</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1474954868777644</v>
+        <v>0.04459228285718848</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4623365257845903</v>
+        <v>0.16267859865238</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.910958904109589</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1393233790300028</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.04246285263122429</v>
+        <v>0.07446620439756768</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.103849975367978</v>
+        <v>0.7002130779721872</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.4208730799854183</v>
+        <v>0.2126389111260971</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.08135951609147174</v>
+        <v>-0.04667270987672878</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.7698246845823712</v>
+        <v>0.7817408110544962</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.0782033666793952</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.03661178759137262</v>
+        <v>-0.03033850606134936</v>
       </c>
       <c r="Z10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.03661178759137274</v>
+        <v>-0.03033850606134936</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.04106454688071903</v>
+        <v>0.01825966162992154</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.04242661271423354</v>
+        <v>-0.002276997264752278</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.001422414043246834</v>
+        <v>0.02058352753056014</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -6663,28 +6672,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393833</v>
+        <v>0.1113578145363061</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.179974191375289</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.240579627043532</v>
+        <v>0.451830499217423</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450096</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6693,10 +6702,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241683001</v>
+        <v>0.5657770181230009</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6705,7 +6714,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174765</v>
+        <v>-0.0518515658788602</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6751,49 +6760,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.1581520768513234</v>
+        <v>-0.007252311911813636</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.09154899325217558</v>
+        <v>-0.1067254172299203</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1771492010844213</v>
+        <v>0.1314438165933432</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2461249587924721</v>
+        <v>0.4802226182450062</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9395711500974658</v>
+        <v>0.9920634920634921</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3398215970939726</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.04345354862296746</v>
+        <v>-0.04246285263122429</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.096795503018999</v>
+        <v>1.103849975367978</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3398215970939727</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.7543016732344996</v>
+        <v>0.4606940487042375</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1411353747440025</v>
+        <v>-0.06711234626801021</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.403795878337594</v>
+        <v>0.8142678722310382</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1049631221034131</v>
+        <v>-0.09631182261186377</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6845,58 +6854,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.06128603667882748</v>
+        <v>0.009125074064342265</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.0002535315041187758</v>
+        <v>-0.09198904181424106</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1145251377344681</v>
+        <v>0.1149439295311541</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1732872931401137</v>
+        <v>0.4227552867946717</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9649122807017544</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.237660847618366</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1045693220900867</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7670652811375739</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3921442095204601</v>
+        <v>0.4217964992394458</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.09444023883315877</v>
+        <v>-0.09195467631537591</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7298014104598676</v>
+        <v>0.7455172015271687</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07741687217408433</v>
+        <v>-0.07820336667939509</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.08363844620116412</v>
+        <v>0.01649702756567994</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1547471850425688</v>
+        <v>0.04430638244290752</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2064396729704477</v>
+        <v>-0.02662949814801885</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -6947,68 +6956,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.161130036272267</v>
+        <v>-0.255726193952719</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2093718237194475</v>
+        <v>-0.3303022696089866</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2998248830871881</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.221044204612225</v>
+        <v>0.2429021408551373</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2044353132824294</v>
+        <v>0.4064463939617625</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8791423001949318</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2859130451141871</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.03465569255812917</v>
+        <v>-0.04246285263122429</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.9228022727731178</v>
+        <v>1.103849975367978</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2975598105527115</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1747448374293208</v>
+        <v>0.09509831364436527</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2358538381731918</v>
+        <v>-0.3006039167970858</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.3252095166276954</v>
+        <v>0.1680844406862966</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.112357824995991</v>
+        <v>-0.05803005623353996</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2756823732437842</v>
+        <v>-0.2502890563456375</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.08165755156861598</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.3303632691272641</v>
+        <v>-0.2502890563456375</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.8578693937504649</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.4610239073873639</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7057,19 +7062,19 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.08016286187956101</v>
+        <v>-0.03231418984808199</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.13306091476256</v>
+        <v>-0.1292761003748668</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3175486291732158</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2027749660361742</v>
+        <v>0.1452896880813708</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2238082320229166</v>
+        <v>0.454925210921581</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>1</v>
@@ -7078,53 +7083,49 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3153408931099985</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.007982938830215169</v>
+        <v>-0.04246285263122429</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.017782496576866</v>
+        <v>1.103849975367978</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3153408931099986</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.3434965355221975</v>
+        <v>0.4238188825466029</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1260845007895862</v>
+        <v>-0.0906630598950624</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.6392654794488257</v>
+        <v>0.7490917251334235</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1062984144517733</v>
+        <v>-0.0782033666793952</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.2057717146946652</v>
+        <v>-0.02524496227690243</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.03708195220596888</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.2341701794964823</v>
+        <v>-0.02524496227690254</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.1332806554216397</v>
+        <v>-0.04106454688071903</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.1018969644271204</v>
+        <v>-0.04242661271423354</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.03494442146551746</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.8578693937504649</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.09630169010005585</v>
-      </c>
+        <v>0.001422414043246611</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7169,58 +7170,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.2701655235076985</v>
+        <v>-0.255726193952719</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1971207634646714</v>
+        <v>-0.3303022696089866</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1717629611374277</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.0599923979452263</v>
+        <v>0.2429021408551373</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1299116416989429</v>
+        <v>0.4064463939617625</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9181286549707602</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.06645906394467849</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3526272075368406</v>
+        <v>-0.04246285263122429</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2145007942188508</v>
+        <v>1.103849975367978</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1717629611374277</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.3605889944952865</v>
+        <v>0.09509831364436527</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1149662251399994</v>
+        <v>-0.3006039167970858</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6710754625212314</v>
+        <v>0.1680844406862966</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.08987434123095572</v>
+        <v>-0.05803005623353996</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.0967173904837324</v>
+        <v>-0.2502890563456375</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.4140737290798737</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2244270097589909</v>
+        <v>-0.2502890563456375</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -7275,67 +7276,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1453485978189122</v>
+        <v>-0.03231418984808199</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.07948181750963457</v>
+        <v>-0.1292761003748668</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.265676705002627</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1390666096562213</v>
+        <v>0.1452896880813708</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1976148830177948</v>
+        <v>0.454925210921581</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9415204678362573</v>
+        <v>1</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2656767050026272</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.06397655376377331</v>
+        <v>-0.04246285263122429</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8574882167457012</v>
+        <v>1.103849975367978</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.265676705002627</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.5597334384210291</v>
+        <v>0.4238188825466029</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.01457293743082211</v>
+        <v>-0.0906630598950624</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.041693955753554</v>
+        <v>0.7490917251334235</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.08987434123095583</v>
+        <v>-0.0782033666793952</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.01105509309901698</v>
+        <v>-0.02524496227690243</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1123103872604259</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.110909222616618</v>
+        <v>-0.02524496227690254</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.07920820423035879</v>
+        <v>-0.04106454688071903</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.0367498603433084</v>
+        <v>-0.04242661271423354</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.1203820895525594</v>
+        <v>0.001422414043246611</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -7383,68 +7384,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1675990242558427</v>
+        <v>-0.2557261939527193</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.1004526650020412</v>
+        <v>-0.3303022696089869</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.08987434123095583</v>
+        <v>-0.3203589150179399</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.01460551116785951</v>
+        <v>0.2429021408551376</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.07355772313357621</v>
+        <v>0.4064463939617626</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.2222222222222222</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.32035891501794</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.465299433644307</v>
+        <v>-0.04246285263122473</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.036483651193696</v>
+        <v>1.10384997536798</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.3203589150179399</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1545482672276273</v>
+        <v>0.09509831364436527</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.248991271179888</v>
+        <v>-0.3006039167970858</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2876226160390776</v>
+        <v>0.1680844406862966</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.08987434123095583</v>
+        <v>-0.05803005623353996</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.008156914444433561</v>
+        <v>-0.2502890563456378</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.5318643768265305</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.3418758672794714</v>
+        <v>-0.2502890563456375</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.1138279886626354</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>-0.1020706911048278</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7493,74 +7490,70 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.09458515242207444</v>
+        <v>-0.03231418984808199</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.03163767957260677</v>
+        <v>-0.1292761003748668</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1147265304421498</v>
+        <v>0.1452896880813708</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.181716086389606</v>
+        <v>0.454925210921581</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9571150097465887</v>
+        <v>1</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.237660847618366</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.1045693220900867</v>
+        <v>-0.04246285263122429</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7670652811375739</v>
+        <v>1.103849975367978</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.4358243952215575</v>
+        <v>0.4238188825466029</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.06602722079903267</v>
+        <v>-0.0906630598950624</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.8110925792694035</v>
+        <v>0.7490917251334235</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.08987434123095572</v>
+        <v>-0.0782033666793952</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.05488650903434789</v>
+        <v>-0.02524496227690243</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1547471850425688</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.1815407708217872</v>
+        <v>-0.02524496227690254</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.03137619321502871</v>
+        <v>-0.04106454688071903</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>0</v>
+        <v>-0.04242661271423354</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.03137619321502871</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.1138279886626354</v>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>-0.01271107771930213</v>
-      </c>
+        <v>0.001422414043246611</v>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7803,28 +7796,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003974344</v>
+        <v>0.06101703543393833</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1038210158252791</v>
+        <v>0.179974191375289</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213005002</v>
+        <v>0.240579627043532</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138072</v>
+        <v>-0.3098313187450096</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7833,10 +7826,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922787</v>
+        <v>0.5373300241683001</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7845,7 +7838,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174765</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7891,49 +7884,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.03832826771717424</v>
+        <v>0.1581520768513234</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.0360185421127458</v>
+        <v>0.09154899325217558</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.09969672440806285</v>
+        <v>0.1771492010844213</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2832775140836015</v>
+        <v>0.2461249587924721</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9395711500974658</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.3398215970939726</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.03914997669357678</v>
+        <v>-0.04345354862296746</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8645301620965504</v>
+        <v>1.096795503018999</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.3398215970939727</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.1928876156683936</v>
+        <v>0.7543016732344996</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.07233654476469098</v>
+        <v>0.1411353747440025</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.6746549474635332</v>
+        <v>1.403795878337594</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.06809052344706434</v>
+        <v>-0.1049631221034131</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -7985,58 +7978,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>0.06128603667882748</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>0.0002535315041187758</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.1145251377344681</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.1732872931401137</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9649122807017544</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.237660847618366</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>0.1045693220900867</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>0.7670652811375739</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.3921442095204601</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.09444023883315877</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.7298014104598676</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.07741687217408433</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.007839081645294566</v>
+        <v>-0.08363844620116412</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.04925058896749901</v>
+        <v>0.1547471850425688</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.05440994859862003</v>
+        <v>-0.2064396729704477</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -8087,67 +8080,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.161130036272267</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>-0.2093718237194475</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.2998248830871881</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.221044204612225</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2044353132824294</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>0.8791423001949318</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2859130451141871</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.03465569255812917</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.9228022727731178</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.2975598105527115</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1747448374293208</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.2358538381731918</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.3252095166276954</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.112357824995991</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.05534625679647376</v>
+        <v>-0.2756823732437842</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2475018201764358</v>
+        <v>0.08165755156861598</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1540322909931993</v>
+        <v>-0.3303632691272641</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.108636171448848</v>
+        <v>0.8578693937504649</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.08322383365112151</v>
+        <v>-0.4610239073873639</v>
       </c>
     </row>
     <row r="6">
@@ -8197,19 +8190,19 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>-0.08016286187956101</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>-0.13306091476256</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3175486291732158</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.2027749660361742</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.2238082320229166</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>1</v>
@@ -8218,52 +8211,52 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3153408931099985</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>-0.007982938830215169</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>1.017782496576866</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3153408931099986</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.3434965355221975</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.1260845007895862</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.6392654794488257</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.1062984144517733</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.007839081645294566</v>
+        <v>-0.2057717146946652</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.04925058896749901</v>
+        <v>0.03708195220596888</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.05440994859862003</v>
+        <v>-0.2341701794964823</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1332806554216397</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1018969644271204</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0</v>
+        <v>-0.03494442146551746</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.108636171448848</v>
+        <v>0.8578693937504649</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.0003678787044887333</v>
+        <v>-0.09630169010005585</v>
       </c>
     </row>
     <row r="7">
@@ -8309,68 +8302,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.2701655235076985</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>0.1971207634646714</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1717629611374277</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>0.0599923979452263</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1299116416989429</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>0.9181286549707602</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.06645906394467849</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.3526272075368406</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.2145007942188508</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1717629611374277</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.3605889944952865</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.1149662251399994</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.6710754625212314</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.08987434123095572</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.05534625679647376</v>
+        <v>0.0967173904837324</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.2475018201764358</v>
+        <v>0.4140737290798737</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1540322909931993</v>
+        <v>-0.2244270097589909</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.02421241003006935</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>-0.01871188688585168</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8419,74 +8408,70 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>0.1453485978189122</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>0.07948181750963457</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.265676705002627</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.1390666096562213</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.1976148830177948</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.9415204678362573</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2656767050026272</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>0.06397655376377331</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>0.8574882167457012</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.265676705002627</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.5597334384210291</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>0.01457293743082211</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>1.041693955753554</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.08987434123095583</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.007839081645294566</v>
+        <v>-0.01105509309901698</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.04925058896749901</v>
+        <v>0.1123103872604259</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.05440994859862003</v>
+        <v>-0.110909222616618</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0</v>
+        <v>0.07920820423035879</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0</v>
+        <v>-0.0367498603433084</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0.02421241003006935</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>0.04067970923593811</v>
-      </c>
+        <v>0.1203820895525594</v>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8531,67 +8516,67 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1675990242558427</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>0.1004526650020412</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>-0.08987434123095583</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>0.01460551116785951</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.07355772313357621</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.465299433644307</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.036483651193696</v>
       </c>
       <c r="T9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1545482672276273</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.248991271179888</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.2876226160390776</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.08987434123095583</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.05534625679647376</v>
+        <v>0.008156914444433561</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.2475018201764358</v>
+        <v>0.5318643768265305</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1540322909931993</v>
+        <v>-0.3418758672794714</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="n">
-        <v>0.108636171448848</v>
+        <v>0.1138279886626354</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.08322383365112151</v>
+        <v>-0.1020706911048278</v>
       </c>
     </row>
     <row r="10">
@@ -8641,73 +8626,73 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>0.09458515242207444</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>0.03163767957260677</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.1147265304421498</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.181716086389606</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.9571150097465887</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.237660847618366</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>0.1045693220900867</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>0.7670652811375739</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.4358243952215575</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.06602722079903267</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.8110925792694035</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.08987434123095572</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.007839081645294566</v>
+        <v>-0.05488650903434789</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.04925058896749901</v>
+        <v>0.1547471850425688</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.05440994859862003</v>
+        <v>-0.1815407708217872</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0</v>
+        <v>0.03137619321502871</v>
       </c>
       <c r="AC10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0</v>
+        <v>0.03137619321502871</v>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>0.108636171448848</v>
+        <v>0.1138279886626354</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>0.0003678787044887333</v>
+        <v>-0.01271107771930213</v>
       </c>
     </row>
   </sheetData>
@@ -8721,7 +8706,1155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651873308</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947872</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138072</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490121</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.03459148845114535</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.03932284233176719</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.1938287231324922</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.09920833586214862</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.2817572713835914</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.1938287231324922</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.03914997669357678</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.8645301620965504</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.1938287231324922</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.1975228332372316</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.07551635546875812</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.6687927458864688</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.06809052344706434</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>-0.008186945345690755</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.04925058896749901</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.05474148398592771</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>0.05143758046804736</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.2475018201764358</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.1571654938993668</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.108636171448848</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.08322383365112151</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>-0.008186945345690755</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.04925058896749901</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.05474148398592771</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.108636171448848</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0.0003678787044887333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>0.05143758046804736</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.2475018201764358</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.1571654938993668</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.02421241003006935</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>-0.01871188688585168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>-0.008186945345690755</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.04925058896749901</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.05474148398592771</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0.02421241003006935</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0.04067970923593811</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>0.05143758046804736</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.2475018201764358</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.1571654938993668</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.108636171448848</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.08322383365112151</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>-0.008186945345690755</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0.04925058896749901</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>-0.05474148398592771</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.108636171448848</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>0.0003678787044887333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8827,24 +9960,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="J2" s="2" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -8875,20 +10006,20 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-131</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.7281976744186046</v>
+        <v>0.473655019412091</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -8922,23 +10053,23 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-120</v>
+        <v>-131</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-57</v>
+        <v>523</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.04137931034482759</v>
+        <v>0.7281976744186046</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8968,19 +10099,21 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="n">
+        <v>-119</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-57</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.04794520547945205</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -9013,24 +10146,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-132</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>0.3625730994152047</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9061,21 +10192,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-132</v>
+      </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9092,37 +10225,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>59</v>
-      </c>
+        <v>-94</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0.1058171745152355</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -9149,27 +10280,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="J9" s="2" t="n">
-        <v>0.3204941860465116</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9196,25 +10325,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>59</v>
+      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
+        <v>0.1059345535219079</v>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.4206896551724138</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9241,25 +10372,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3204941860465116</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9286,24 +10419,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>119</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J12" s="2" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -9333,27 +10464,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>58</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -9370,24 +10499,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -9397,10 +10526,10 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>0.313573407202216</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9417,37 +10546,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>59</v>
+        <v>-30</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.4585755813953488</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -9474,25 +10603,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -9519,25 +10650,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>183</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3139212423738214</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -9564,27 +10697,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-63</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.7309941520467836</v>
+        <v>0.4585755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -9611,32 +10744,169 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>58</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-63</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.7309941520467836</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-94</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>94</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
